--- a/artfynd/A 21734-2023 artfynd.xlsx
+++ b/artfynd/A 21734-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21734-2023 artfynd.xlsx
+++ b/artfynd/A 21734-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>112079714</v>
       </c>
       <c r="B2" t="n">
-        <v>85435</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,7 +713,7 @@
         <v>596310</v>
       </c>
       <c r="R2" t="n">
-        <v>6572446</v>
+        <v>6572447</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,48 +776,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112757191</v>
+        <v>112757997</v>
       </c>
       <c r="B3" t="n">
-        <v>91199</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Åsborgen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596302</v>
+        <v>596349</v>
       </c>
       <c r="R3" t="n">
         <v>6572463</v>
@@ -866,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -888,37 +881,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112757187</v>
+        <v>112758176</v>
       </c>
       <c r="B4" t="n">
-        <v>104224</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>3100</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596302</v>
+        <v>596361</v>
       </c>
       <c r="R4" t="n">
-        <v>6572463</v>
+        <v>6572440</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,37 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112757739</v>
+        <v>112757191</v>
       </c>
       <c r="B5" t="n">
-        <v>91211</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1019,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596285</v>
+        <v>596303</v>
       </c>
       <c r="R5" t="n">
-        <v>6572495</v>
+        <v>6572462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,6 +1078,617 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>112757739</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Åsborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596286</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6572495</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson, Ylva Linnman, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>112757801</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åsborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596331</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6572480</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson, Ylva Linnman, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112758092</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åsborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>596349</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6572463</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson, Ylva Linnman, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>112758181</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Åsborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>596361</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6572440</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson, Ylva Linnman, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>112079715</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ärla, åsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>596383</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6572388</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>112757187</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Åsborgen, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>596303</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6572462</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ärla</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fredrik Enoksson, Ylva Linnman, Ralf Lundmark</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
         </is>

--- a/artfynd/A 21734-2023 artfynd.xlsx
+++ b/artfynd/A 21734-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Lst D inventering sandbarrskogar</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079714</t>
         </is>
       </c>
     </row>
@@ -878,6 +888,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112757997</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112758176</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112757191</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112757739</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112757801</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112758092</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112758181</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112079715</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,8 +1743,25 @@
           <t>Lst D inventering sandbarrskogar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112757187</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>